--- a/human_validation/judge/en/judge_D022_S003_P001__qwen3-235b.xlsx
+++ b/human_validation/judge/en/judge_D022_S003_P001__qwen3-235b.xlsx
@@ -461,6 +461,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -504,7 +505,9 @@
           <t>IAS (mean over turns)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
+      <c r="B7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -554,6 +557,7 @@
         <v>0.1111</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
